--- a/reports/jobs_2026-08-31.xlsx
+++ b/reports/jobs_2026-08-31.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Software Developer, Full Stack (Bangkok-based, 6-month Contract) Technology Bangkok, Thailand</t>
+          <t>GPU Hardware Analysis and Automation Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/job/6883264-software-developer-full-stack-bangkok-based-6-month-contract/</t>
+          <t>https://careers.arm.com/job/trondheim/gpu-hardware-analysis-and-automation-engineer/33099/94973985632</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UCIe/D2D Post Si Validation Engineer</t>
+          <t>Software Engineer – CI/CD, Release &amp; Automation</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/bengaluru/ucie-d2d-post-si-validation-engineer/33099/98165857552</t>
+          <t>https://careers.arm.com/job/bengaluru/software-engineer-ci-cd-release-and-automation/33099/99971290032</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -608,66 +608,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Rubrik India</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer - IAM</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Software Developer, Full Stack (Bangkok-based, 6-month Contract) Technology Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -683,12 +679,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/job/6883264-software-developer-full-stack-bangkok-based-6-month-contract/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -1570,7 +1566,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Tech Support Intern</t>
+          <t>Product Support Intern (API Integration)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1595,7 +1591,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-698555-tech-support-intern</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1617,12 +1613,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Product Support Intern (API Integration)</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1632,7 +1628,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru/ Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1642,7 +1638,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1852,7 +1848,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1867,7 +1863,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1877,7 +1873,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1899,12 +1895,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1914,7 +1910,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru Full-time</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1924,7 +1920,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1946,12 +1942,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1971,7 +1967,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1993,7 +1989,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2008,7 +2004,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bangalore Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2018,7 +2014,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2040,12 +2036,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2055,7 +2051,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore Full-time</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2065,7 +2061,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2082,17 +2078,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2102,7 +2098,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2112,12 +2108,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2134,7 +2130,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2159,7 +2155,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2181,7 +2177,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2206,7 +2202,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2223,17 +2219,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2243,7 +2239,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Chennai, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2253,12 +2249,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2270,17 +2266,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>SharePoint Full Stack role</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2296,12 +2292,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2313,12 +2309,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>UI Developer - Digital Products</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2339,12 +2335,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2356,17 +2352,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2376,7 +2372,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Chennai, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2386,12 +2382,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2403,17 +2399,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2421,11 +2417,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2433,12 +2425,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2450,17 +2442,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2468,11 +2460,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2480,12 +2468,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2497,17 +2485,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2517,7 +2505,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2527,12 +2515,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2544,17 +2532,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2564,7 +2552,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2574,12 +2562,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2591,17 +2579,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2609,7 +2597,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2617,12 +2609,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2634,17 +2626,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2652,7 +2644,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2660,12 +2656,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2677,17 +2673,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2695,7 +2691,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2703,12 +2703,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2720,17 +2720,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Licious</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>By: Licious DevOps</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://careers.licious.com/author/adminlic/</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://www.licious.in/careers</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2763,17 +2763,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2806,17 +2806,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2849,17 +2849,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Operations - Internship</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2867,11 +2867,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2879,12 +2875,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6c1b9af2-9a7c-4cd2-a97b-54e956cf82f1</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2896,17 +2892,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2914,11 +2910,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2926,12 +2918,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2943,12 +2935,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2961,11 +2953,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -2973,12 +2961,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2995,7 +2983,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3005,12 +2993,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3020,7 +3008,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3042,7 +3030,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Paytm Gold</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3067,7 +3055,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/c98325df-98c4-4966-8630-4ceaa7e55909</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3089,7 +3077,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3099,7 +3087,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -3114,7 +3102,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3131,17 +3119,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3149,7 +3137,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -3157,12 +3149,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3174,17 +3166,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3192,11 +3184,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -3204,12 +3192,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3226,12 +3214,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3251,7 +3239,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3273,12 +3261,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3298,7 +3286,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3315,17 +3303,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3333,7 +3321,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -3341,12 +3333,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3358,17 +3350,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3376,11 +3368,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -3388,12 +3376,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3410,12 +3398,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3435,7 +3423,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3452,17 +3440,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3472,7 +3460,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3482,12 +3470,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3499,17 +3487,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Product Operations &amp; Analytics Intern</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3519,7 +3507,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3529,12 +3517,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3546,17 +3534,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Vision</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3566,7 +3554,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3576,12 +3564,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3593,17 +3581,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Product Operations &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3613,7 +3601,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3623,12 +3611,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3640,17 +3628,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3658,7 +3646,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -3666,12 +3658,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3688,12 +3680,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3709,7 +3701,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3752,7 +3744,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -3774,7 +3766,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3795,7 +3787,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -3812,17 +3804,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3830,11 +3822,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -3842,12 +3830,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3864,12 +3852,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3889,7 +3877,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -3906,17 +3894,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3926,7 +3914,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3936,12 +3924,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3953,17 +3941,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3971,7 +3959,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>CO-Colombia-Remote</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -3979,12 +3971,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3996,12 +3988,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -4014,11 +4006,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -4026,12 +4014,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4043,17 +4031,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4063,7 +4051,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4073,12 +4061,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4095,12 +4083,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4120,7 +4108,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4137,48 +4125,95 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
           <t>upGrad</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Data Science Bootcamp with AI</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4260,6 +4295,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4271,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4359,15 +4395,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Vymo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://getvymo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4376,26 +4432,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Darwinbox</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://darwinbox.com/careers</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -4439,35 +4475,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FirstCry</t>
+          <t>MakeMyTrip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.firstcry.com/careers</t>
+          <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MakeMyTrip</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://careers.makemytrip.com/</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4476,6 +4492,26 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OYO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.oyorooms.com/careers/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -4499,15 +4535,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4516,18 +4572,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4536,18 +4592,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
